--- a/nursing/フォーマット/02_訪問看護記録様式/03_訪問看護記録書Ⅱ経過記録.xlsx
+++ b/nursing/フォーマット/02_訪問看護記録様式/03_訪問看護記録書Ⅱ経過記録.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,8 +28,14 @@
     <font>
       <name val="Meiryo UI"/>
       <b val="1"/>
-      <color rgb="000E7490"/>
-      <sz val="14"/>
+      <color rgb="FF0E7490"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
+      <color rgb="FFDC2626"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Meiryo UI"/>
@@ -39,23 +45,22 @@
     <font>
       <name val="Meiryo UI"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Meiryo UI"/>
       <i val="1"/>
-      <color rgb="006B7280"/>
+      <color rgb="FF6B7280"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Meiryo UI"/>
-      <sz val="9"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Meiryo UI"/>
-      <b val="1"/>
-      <color rgb="00DC2626"/>
+      <color rgb="FF6B7280"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -68,12 +73,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000E7490"/>
+        <fgColor rgb="FF0E7490"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8FAFC"/>
+        <fgColor rgb="FFF8FAFC"/>
       </patternFill>
     </fill>
   </fills>
@@ -95,24 +100,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -480,21 +489,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="52" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -507,445 +519,588 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>【修正方法】修正液使用禁止。二重線で消し、訂正者署名・日付を記入。遡及記録・追記禁止。【保管】5年間</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
           <t>利用者氏名：</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>生年月日：</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>（　　　）年度</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>（　　　　）年度</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>訪問日</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>開始時刻</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>終了時刻</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>訪問
+職種</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>開始
+時刻</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>終了
+時刻</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>体温
 (℃)</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>血圧
 (mmHg)</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>脈拍
 (/分)</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>SpO2
 (%)</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>呼吸
 (/分)</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>訪問看護の内容・利用者の状態・反応（SOAPまたは自由記述）</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>特記事項・連絡事項</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>次回訪問予定</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>疼痛
+NRS</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>意識
+(JCS)</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>訪問看護の内容・利用者の状態
+（S：主観 O：客観 A：評価 P：計画）</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>実施した
+看護・リハ内容</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>特記事項・
+連絡事項</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>記録者</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="5" ht="80" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>5/1(木)</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>看護師</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>36.5</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>120/80</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>128/76</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>【S】特に問題なし。昨日の夜は眠れたとのこと。【O】顔色良好。痰の喀出あり。吸引実施、少量の白色痰。【A】バイタル安定。誤嚥リスク継続。【P】引き続き観察継続。</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>主治医への報告不要。次回も同様のケアを継続。</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>5/8(木) 10:00</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>【S】昨夜は眠れた。足のむくみが気になると本人。
+【O】顔色良好。両下腿浮腫(+)右&gt;左。褥瘡なし。排泄自立。服薬確認済み。
+【A】バイタル安定。浮腫は前回比不変。誤嚥リスク継続観察要。
+【P】次回も同様のケア継続。排泄状況・浮腫を継続観察。</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>バイタル測定・清拭介助・服薬確認・褥瘡観察・患者教育（水分摂取促進）</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>主治医報告不要。家族（長男）より電話で状況確認→問題なし。</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
         <is>
           <t>山田 看護師</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="5" t="inlineStr"/>
-      <c r="B5" s="5" t="inlineStr"/>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
-      <c r="L5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="5" t="inlineStr"/>
-      <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
-      <c r="L6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="5" t="inlineStr"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="5" t="inlineStr"/>
-      <c r="K7" s="5" t="inlineStr"/>
-      <c r="L7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="5" t="inlineStr"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="inlineStr"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="5" t="inlineStr"/>
-      <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr"/>
-      <c r="K8" s="5" t="inlineStr"/>
-      <c r="L8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9" ht="45" customHeight="1">
-      <c r="A9" s="5" t="inlineStr"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="inlineStr"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="5" t="inlineStr"/>
-      <c r="G9" s="5" t="inlineStr"/>
-      <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr"/>
-      <c r="K9" s="5" t="inlineStr"/>
-      <c r="L9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10" ht="45" customHeight="1">
-      <c r="A10" s="5" t="inlineStr"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
-      <c r="L10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="5" t="inlineStr"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
-      <c r="L11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="5" t="inlineStr"/>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
-      <c r="L12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13" ht="45" customHeight="1">
-      <c r="A13" s="5" t="inlineStr"/>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="inlineStr"/>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="inlineStr"/>
-      <c r="F13" s="5" t="inlineStr"/>
-      <c r="G13" s="5" t="inlineStr"/>
-      <c r="H13" s="5" t="inlineStr"/>
-      <c r="I13" s="5" t="inlineStr"/>
-      <c r="J13" s="5" t="inlineStr"/>
-      <c r="K13" s="5" t="inlineStr"/>
-      <c r="L13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14" ht="45" customHeight="1">
-      <c r="A14" s="5" t="inlineStr"/>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="inlineStr"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="5" t="inlineStr"/>
-      <c r="G14" s="5" t="inlineStr"/>
-      <c r="H14" s="5" t="inlineStr"/>
-      <c r="I14" s="5" t="inlineStr"/>
-      <c r="J14" s="5" t="inlineStr"/>
-      <c r="K14" s="5" t="inlineStr"/>
-      <c r="L14" s="5" t="inlineStr"/>
-    </row>
-    <row r="15" ht="45" customHeight="1">
-      <c r="A15" s="5" t="inlineStr"/>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="5" t="inlineStr"/>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="5" t="inlineStr"/>
-      <c r="G15" s="5" t="inlineStr"/>
-      <c r="H15" s="5" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="5" t="inlineStr"/>
-      <c r="K15" s="5" t="inlineStr"/>
-      <c r="L15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16" ht="45" customHeight="1">
-      <c r="A16" s="5" t="inlineStr"/>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
-      <c r="L16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17" ht="45" customHeight="1">
-      <c r="A17" s="5" t="inlineStr"/>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
-      <c r="L17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18" ht="45" customHeight="1">
-      <c r="A18" s="5" t="inlineStr"/>
-      <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
-      <c r="L18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19" ht="45" customHeight="1">
-      <c r="A19" s="5" t="inlineStr"/>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="5" t="inlineStr"/>
-      <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="5" t="inlineStr"/>
-      <c r="F19" s="5" t="inlineStr"/>
-      <c r="G19" s="5" t="inlineStr"/>
-      <c r="H19" s="5" t="inlineStr"/>
-      <c r="I19" s="5" t="inlineStr"/>
-      <c r="J19" s="5" t="inlineStr"/>
-      <c r="K19" s="5" t="inlineStr"/>
-      <c r="L19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="5" t="inlineStr"/>
-      <c r="B20" s="5" t="inlineStr"/>
-      <c r="C20" s="5" t="inlineStr"/>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="5" t="inlineStr"/>
-      <c r="F20" s="5" t="inlineStr"/>
-      <c r="G20" s="5" t="inlineStr"/>
-      <c r="H20" s="5" t="inlineStr"/>
-      <c r="I20" s="5" t="inlineStr"/>
-      <c r="J20" s="5" t="inlineStr"/>
-      <c r="K20" s="5" t="inlineStr"/>
-      <c r="L20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="5" t="inlineStr"/>
-      <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="5" t="inlineStr"/>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="5" t="inlineStr"/>
-      <c r="F21" s="5" t="inlineStr"/>
-      <c r="G21" s="5" t="inlineStr"/>
-      <c r="H21" s="5" t="inlineStr"/>
-      <c r="I21" s="5" t="inlineStr"/>
-      <c r="J21" s="5" t="inlineStr"/>
-      <c r="K21" s="5" t="inlineStr"/>
-      <c r="L21" s="5" t="inlineStr"/>
-    </row>
-    <row r="22" ht="45" customHeight="1">
-      <c r="A22" s="5" t="inlineStr"/>
-      <c r="B22" s="5" t="inlineStr"/>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
-      <c r="L22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23" ht="45" customHeight="1">
-      <c r="A23" s="5" t="inlineStr"/>
-      <c r="B23" s="5" t="inlineStr"/>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
-      <c r="L23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24" ht="45" customHeight="1">
-      <c r="A24" s="5" t="inlineStr"/>
-      <c r="B24" s="5" t="inlineStr"/>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
-      <c r="L24" s="5" t="inlineStr"/>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>※ 修正は二重線で消し、訂正者の署名・日付を記入してください。修正液（白塗り）の使用は禁止です。</t>
+    <row r="6" ht="50" customHeight="1">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="7" t="n"/>
+      <c r="M6" s="7" t="n"/>
+      <c r="N6" s="7" t="n"/>
+      <c r="O6" s="7" t="n"/>
+    </row>
+    <row r="7" ht="50" customHeight="1">
+      <c r="A7" s="6" t="n"/>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="7" t="n"/>
+      <c r="M7" s="7" t="n"/>
+      <c r="N7" s="7" t="n"/>
+      <c r="O7" s="7" t="n"/>
+    </row>
+    <row r="8" ht="50" customHeight="1">
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="6" t="n"/>
+      <c r="L8" s="7" t="n"/>
+      <c r="M8" s="7" t="n"/>
+      <c r="N8" s="7" t="n"/>
+      <c r="O8" s="7" t="n"/>
+    </row>
+    <row r="9" ht="50" customHeight="1">
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="7" t="n"/>
+      <c r="M9" s="7" t="n"/>
+      <c r="N9" s="7" t="n"/>
+      <c r="O9" s="7" t="n"/>
+    </row>
+    <row r="10" ht="50" customHeight="1">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="6" t="n"/>
+      <c r="K10" s="6" t="n"/>
+      <c r="L10" s="7" t="n"/>
+      <c r="M10" s="7" t="n"/>
+      <c r="N10" s="7" t="n"/>
+      <c r="O10" s="7" t="n"/>
+    </row>
+    <row r="11" ht="50" customHeight="1">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="7" t="n"/>
+      <c r="M11" s="7" t="n"/>
+      <c r="N11" s="7" t="n"/>
+      <c r="O11" s="7" t="n"/>
+    </row>
+    <row r="12" ht="50" customHeight="1">
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n"/>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="6" t="n"/>
+      <c r="L12" s="7" t="n"/>
+      <c r="M12" s="7" t="n"/>
+      <c r="N12" s="7" t="n"/>
+      <c r="O12" s="7" t="n"/>
+    </row>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n"/>
+      <c r="J13" s="6" t="n"/>
+      <c r="K13" s="6" t="n"/>
+      <c r="L13" s="7" t="n"/>
+      <c r="M13" s="7" t="n"/>
+      <c r="N13" s="7" t="n"/>
+      <c r="O13" s="7" t="n"/>
+    </row>
+    <row r="14" ht="50" customHeight="1">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="6" t="n"/>
+      <c r="L14" s="7" t="n"/>
+      <c r="M14" s="7" t="n"/>
+      <c r="N14" s="7" t="n"/>
+      <c r="O14" s="7" t="n"/>
+    </row>
+    <row r="15" ht="50" customHeight="1">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="6" t="n"/>
+      <c r="L15" s="7" t="n"/>
+      <c r="M15" s="7" t="n"/>
+      <c r="N15" s="7" t="n"/>
+      <c r="O15" s="7" t="n"/>
+    </row>
+    <row r="16" ht="50" customHeight="1">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n"/>
+      <c r="J16" s="6" t="n"/>
+      <c r="K16" s="6" t="n"/>
+      <c r="L16" s="7" t="n"/>
+      <c r="M16" s="7" t="n"/>
+      <c r="N16" s="7" t="n"/>
+      <c r="O16" s="7" t="n"/>
+    </row>
+    <row r="17" ht="50" customHeight="1">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="6" t="n"/>
+      <c r="L17" s="7" t="n"/>
+      <c r="M17" s="7" t="n"/>
+      <c r="N17" s="7" t="n"/>
+      <c r="O17" s="7" t="n"/>
+    </row>
+    <row r="18" ht="50" customHeight="1">
+      <c r="A18" s="6" t="n"/>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
+      <c r="L18" s="7" t="n"/>
+      <c r="M18" s="7" t="n"/>
+      <c r="N18" s="7" t="n"/>
+      <c r="O18" s="7" t="n"/>
+    </row>
+    <row r="19" ht="50" customHeight="1">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="6" t="n"/>
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="6" t="n"/>
+      <c r="L19" s="7" t="n"/>
+      <c r="M19" s="7" t="n"/>
+      <c r="N19" s="7" t="n"/>
+      <c r="O19" s="7" t="n"/>
+    </row>
+    <row r="20" ht="50" customHeight="1">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
+      <c r="J20" s="6" t="n"/>
+      <c r="K20" s="6" t="n"/>
+      <c r="L20" s="7" t="n"/>
+      <c r="M20" s="7" t="n"/>
+      <c r="N20" s="7" t="n"/>
+      <c r="O20" s="7" t="n"/>
+    </row>
+    <row r="21" ht="50" customHeight="1">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n"/>
+      <c r="J21" s="6" t="n"/>
+      <c r="K21" s="6" t="n"/>
+      <c r="L21" s="7" t="n"/>
+      <c r="M21" s="7" t="n"/>
+      <c r="N21" s="7" t="n"/>
+      <c r="O21" s="7" t="n"/>
+    </row>
+    <row r="22" ht="50" customHeight="1">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="6" t="n"/>
+      <c r="L22" s="7" t="n"/>
+      <c r="M22" s="7" t="n"/>
+      <c r="N22" s="7" t="n"/>
+      <c r="O22" s="7" t="n"/>
+    </row>
+    <row r="23" ht="50" customHeight="1">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n"/>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="6" t="n"/>
+      <c r="L23" s="7" t="n"/>
+      <c r="M23" s="7" t="n"/>
+      <c r="N23" s="7" t="n"/>
+      <c r="O23" s="7" t="n"/>
+    </row>
+    <row r="24" ht="50" customHeight="1">
+      <c r="A24" s="6" t="n"/>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="6" t="n"/>
+      <c r="J24" s="6" t="n"/>
+      <c r="K24" s="6" t="n"/>
+      <c r="L24" s="7" t="n"/>
+      <c r="M24" s="7" t="n"/>
+      <c r="N24" s="7" t="n"/>
+      <c r="O24" s="7" t="n"/>
+    </row>
+    <row r="25" ht="50" customHeight="1">
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="6" t="n"/>
+      <c r="J25" s="6" t="n"/>
+      <c r="K25" s="6" t="n"/>
+      <c r="L25" s="7" t="n"/>
+      <c r="M25" s="7" t="n"/>
+      <c r="N25" s="7" t="n"/>
+      <c r="O25" s="7" t="n"/>
+    </row>
+    <row r="26" ht="50" customHeight="1">
+      <c r="A26" s="6" t="n"/>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="6" t="n"/>
+      <c r="J26" s="6" t="n"/>
+      <c r="K26" s="6" t="n"/>
+      <c r="L26" s="7" t="n"/>
+      <c r="M26" s="7" t="n"/>
+      <c r="N26" s="7" t="n"/>
+      <c r="O26" s="7" t="n"/>
+    </row>
+    <row r="27" ht="50" customHeight="1">
+      <c r="A27" s="6" t="n"/>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="6" t="n"/>
+      <c r="J27" s="6" t="n"/>
+      <c r="K27" s="6" t="n"/>
+      <c r="L27" s="7" t="n"/>
+      <c r="M27" s="7" t="n"/>
+      <c r="N27" s="7" t="n"/>
+      <c r="O27" s="7" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>【訪問職種凡例】看：看護師　准：准看護師　PT：理学療法士　OT：作業療法士　ST：言語聴覚士　【疼痛NRS】0=痛みなし〜10=最大の痛み　【意識JCS】0=清明　1〜3桁=障害あり</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:C2"/>
+  <mergeCells count="8">
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="A28:O28"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="I3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>

--- a/nursing/フォーマット/02_訪問看護記録様式/03_訪問看護記録書Ⅱ経過記録.xlsx
+++ b/nursing/フォーマット/02_訪問看護記録様式/03_訪問看護記録書Ⅱ経過記録.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="訪問看護記録書Ⅱ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="経過記録" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,42 +26,32 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
       <b val="1"/>
-      <color rgb="FF0E7490"/>
-      <sz val="13"/>
+      <color rgb="00163A2B"/>
+      <sz val="16"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <b val="1"/>
-      <color rgb="FFDC2626"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Meiryo UI"/>
-      <b val="1"/>
+      <name val="Meiryo"/>
+      <color rgb="005C665C"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <i val="1"/>
-      <color rgb="FF6B7280"/>
-      <sz val="9"/>
+      <name val="Meiryo"/>
+      <color rgb="00283129"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Meiryo UI"/>
-      <color rgb="FF6B7280"/>
-      <sz val="8"/>
+      <name val="Meiryo"/>
+      <i val="1"/>
+      <color rgb="005C665C"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="4">
@@ -73,16 +63,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0E7490"/>
+        <fgColor rgb="00A9854A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8FAFC"/>
+        <fgColor rgb="00F6EDDA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -91,10 +81,42 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <bottom style="medium">
+        <color rgb="00A9854A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A9854A"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A9854A"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A9854A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A9854A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00DAD3C2"/>
+      </left>
+      <right style="thin">
+        <color rgb="00DAD3C2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DAD3C2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DAD3C2"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00A9854A"/>
+      </left>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -103,27 +125,25 @@
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,60 +507,46 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="5" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="52" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>訪問看護記録書Ⅱ（経過記録）</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>【修正方法】修正液使用禁止。二重線で消し、訂正者署名・日付を記入。遡及記録・追記禁止。【保管】5年間</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>利用者氏名：</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>生年月日：</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>（　　　　）年度</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
+          <t>訪問ごとにバイタル・観察・実施したケア・利用者の状態・特記を記録（指示書に沿った内容）</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>訪問日</t>
@@ -548,169 +554,93 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>訪問
-職種</t>
+          <t>時間</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>開始
-時刻</t>
+          <t>体温</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>終了
-時刻</t>
+          <t>血圧</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>体温
-(℃)</t>
+          <t>脈拍</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>血圧
-(mmHg)</t>
+          <t>SpO2</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>脈拍
-(/分)</t>
+          <t>観察・状態</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>SpO2
-(%)</t>
+          <t>実施したケア・指導</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>呼吸
-(/分)</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>疼痛
-NRS</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>意識
-(JCS)</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>訪問看護の内容・利用者の状態
-（S：主観 O：客観 A：評価 P：計画）</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>実施した
-看護・リハ内容</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>特記事項・
-連絡事項</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
           <t>記録者</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="80" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>5/1(木)</t>
+          <t>（例）6/2</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>看護師</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>128/78</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>128/76</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>顔色良好。食欲あり。</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>服薬確認・血圧測定・清拭。次回まで水分摂取を促す。</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>【S】昨夜は眠れた。足のむくみが気になると本人。
-【O】顔色良好。両下腿浮腫(+)右&gt;左。褥瘡なし。排泄自立。服薬確認済み。
-【A】バイタル安定。浮腫は前回比不変。誤嚥リスク継続観察要。
-【P】次回も同様のケア継続。排泄状況・浮腫を継続観察。</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>バイタル測定・清拭介助・服薬確認・褥瘡観察・患者教育（水分摂取促進）</t>
-        </is>
-      </c>
-      <c r="N5" s="5" t="inlineStr">
-        <is>
-          <t>主治医報告不要。家族（長男）より電話で状況確認→問題なし。</t>
-        </is>
-      </c>
-      <c r="O5" s="5" t="inlineStr">
-        <is>
-          <t>山田 看護師</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="50" customHeight="1">
+          <t>看護師A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="6" t="n"/>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
@@ -720,14 +650,8 @@
       <c r="G6" s="6" t="n"/>
       <c r="H6" s="6" t="n"/>
       <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="7" t="n"/>
-      <c r="M6" s="7" t="n"/>
-      <c r="N6" s="7" t="n"/>
-      <c r="O6" s="7" t="n"/>
-    </row>
-    <row r="7" ht="50" customHeight="1">
+    </row>
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="6" t="n"/>
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="6" t="n"/>
@@ -737,14 +661,8 @@
       <c r="G7" s="6" t="n"/>
       <c r="H7" s="6" t="n"/>
       <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="7" t="n"/>
-      <c r="M7" s="7" t="n"/>
-      <c r="N7" s="7" t="n"/>
-      <c r="O7" s="7" t="n"/>
-    </row>
-    <row r="8" ht="50" customHeight="1">
+    </row>
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="6" t="n"/>
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
@@ -754,14 +672,8 @@
       <c r="G8" s="6" t="n"/>
       <c r="H8" s="6" t="n"/>
       <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="7" t="n"/>
-      <c r="M8" s="7" t="n"/>
-      <c r="N8" s="7" t="n"/>
-      <c r="O8" s="7" t="n"/>
-    </row>
-    <row r="9" ht="50" customHeight="1">
+    </row>
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="6" t="n"/>
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
@@ -771,14 +683,8 @@
       <c r="G9" s="6" t="n"/>
       <c r="H9" s="6" t="n"/>
       <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="7" t="n"/>
-      <c r="M9" s="7" t="n"/>
-      <c r="N9" s="7" t="n"/>
-      <c r="O9" s="7" t="n"/>
-    </row>
-    <row r="10" ht="50" customHeight="1">
+    </row>
+    <row r="10" ht="30" customHeight="1">
       <c r="A10" s="6" t="n"/>
       <c r="B10" s="6" t="n"/>
       <c r="C10" s="6" t="n"/>
@@ -788,14 +694,8 @@
       <c r="G10" s="6" t="n"/>
       <c r="H10" s="6" t="n"/>
       <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="7" t="n"/>
-      <c r="M10" s="7" t="n"/>
-      <c r="N10" s="7" t="n"/>
-      <c r="O10" s="7" t="n"/>
-    </row>
-    <row r="11" ht="50" customHeight="1">
+    </row>
+    <row r="11" ht="30" customHeight="1">
       <c r="A11" s="6" t="n"/>
       <c r="B11" s="6" t="n"/>
       <c r="C11" s="6" t="n"/>
@@ -805,14 +705,8 @@
       <c r="G11" s="6" t="n"/>
       <c r="H11" s="6" t="n"/>
       <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="7" t="n"/>
-      <c r="M11" s="7" t="n"/>
-      <c r="N11" s="7" t="n"/>
-      <c r="O11" s="7" t="n"/>
-    </row>
-    <row r="12" ht="50" customHeight="1">
+    </row>
+    <row r="12" ht="30" customHeight="1">
       <c r="A12" s="6" t="n"/>
       <c r="B12" s="6" t="n"/>
       <c r="C12" s="6" t="n"/>
@@ -822,14 +716,8 @@
       <c r="G12" s="6" t="n"/>
       <c r="H12" s="6" t="n"/>
       <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="7" t="n"/>
-      <c r="M12" s="7" t="n"/>
-      <c r="N12" s="7" t="n"/>
-      <c r="O12" s="7" t="n"/>
-    </row>
-    <row r="13" ht="50" customHeight="1">
+    </row>
+    <row r="13" ht="30" customHeight="1">
       <c r="A13" s="6" t="n"/>
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n"/>
@@ -839,14 +727,8 @@
       <c r="G13" s="6" t="n"/>
       <c r="H13" s="6" t="n"/>
       <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="7" t="n"/>
-      <c r="M13" s="7" t="n"/>
-      <c r="N13" s="7" t="n"/>
-      <c r="O13" s="7" t="n"/>
-    </row>
-    <row r="14" ht="50" customHeight="1">
+    </row>
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" s="6" t="n"/>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
@@ -856,14 +738,8 @@
       <c r="G14" s="6" t="n"/>
       <c r="H14" s="6" t="n"/>
       <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="7" t="n"/>
-      <c r="M14" s="7" t="n"/>
-      <c r="N14" s="7" t="n"/>
-      <c r="O14" s="7" t="n"/>
-    </row>
-    <row r="15" ht="50" customHeight="1">
+    </row>
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="6" t="n"/>
       <c r="B15" s="6" t="n"/>
       <c r="C15" s="6" t="n"/>
@@ -873,14 +749,8 @@
       <c r="G15" s="6" t="n"/>
       <c r="H15" s="6" t="n"/>
       <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="7" t="n"/>
-      <c r="M15" s="7" t="n"/>
-      <c r="N15" s="7" t="n"/>
-      <c r="O15" s="7" t="n"/>
-    </row>
-    <row r="16" ht="50" customHeight="1">
+    </row>
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="6" t="n"/>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
@@ -890,14 +760,8 @@
       <c r="G16" s="6" t="n"/>
       <c r="H16" s="6" t="n"/>
       <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="7" t="n"/>
-      <c r="M16" s="7" t="n"/>
-      <c r="N16" s="7" t="n"/>
-      <c r="O16" s="7" t="n"/>
-    </row>
-    <row r="17" ht="50" customHeight="1">
+    </row>
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="6" t="n"/>
       <c r="B17" s="6" t="n"/>
       <c r="C17" s="6" t="n"/>
@@ -907,14 +771,8 @@
       <c r="G17" s="6" t="n"/>
       <c r="H17" s="6" t="n"/>
       <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="7" t="n"/>
-      <c r="M17" s="7" t="n"/>
-      <c r="N17" s="7" t="n"/>
-      <c r="O17" s="7" t="n"/>
-    </row>
-    <row r="18" ht="50" customHeight="1">
+    </row>
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="6" t="n"/>
       <c r="B18" s="6" t="n"/>
       <c r="C18" s="6" t="n"/>
@@ -924,14 +782,8 @@
       <c r="G18" s="6" t="n"/>
       <c r="H18" s="6" t="n"/>
       <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="6" t="n"/>
-      <c r="L18" s="7" t="n"/>
-      <c r="M18" s="7" t="n"/>
-      <c r="N18" s="7" t="n"/>
-      <c r="O18" s="7" t="n"/>
-    </row>
-    <row r="19" ht="50" customHeight="1">
+    </row>
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="6" t="n"/>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
@@ -941,14 +793,8 @@
       <c r="G19" s="6" t="n"/>
       <c r="H19" s="6" t="n"/>
       <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="6" t="n"/>
-      <c r="L19" s="7" t="n"/>
-      <c r="M19" s="7" t="n"/>
-      <c r="N19" s="7" t="n"/>
-      <c r="O19" s="7" t="n"/>
-    </row>
-    <row r="20" ht="50" customHeight="1">
+    </row>
+    <row r="20" ht="30" customHeight="1">
       <c r="A20" s="6" t="n"/>
       <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="n"/>
@@ -958,151 +804,29 @@
       <c r="G20" s="6" t="n"/>
       <c r="H20" s="6" t="n"/>
       <c r="I20" s="6" t="n"/>
-      <c r="J20" s="6" t="n"/>
-      <c r="K20" s="6" t="n"/>
-      <c r="L20" s="7" t="n"/>
-      <c r="M20" s="7" t="n"/>
-      <c r="N20" s="7" t="n"/>
-      <c r="O20" s="7" t="n"/>
-    </row>
-    <row r="21" ht="50" customHeight="1">
-      <c r="A21" s="6" t="n"/>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
-      <c r="I21" s="6" t="n"/>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="6" t="n"/>
-      <c r="L21" s="7" t="n"/>
-      <c r="M21" s="7" t="n"/>
-      <c r="N21" s="7" t="n"/>
-      <c r="O21" s="7" t="n"/>
-    </row>
-    <row r="22" ht="50" customHeight="1">
-      <c r="A22" s="6" t="n"/>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
-      <c r="I22" s="6" t="n"/>
-      <c r="J22" s="6" t="n"/>
-      <c r="K22" s="6" t="n"/>
-      <c r="L22" s="7" t="n"/>
-      <c r="M22" s="7" t="n"/>
-      <c r="N22" s="7" t="n"/>
-      <c r="O22" s="7" t="n"/>
-    </row>
-    <row r="23" ht="50" customHeight="1">
-      <c r="A23" s="6" t="n"/>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
-      <c r="I23" s="6" t="n"/>
-      <c r="J23" s="6" t="n"/>
-      <c r="K23" s="6" t="n"/>
-      <c r="L23" s="7" t="n"/>
-      <c r="M23" s="7" t="n"/>
-      <c r="N23" s="7" t="n"/>
-      <c r="O23" s="7" t="n"/>
-    </row>
-    <row r="24" ht="50" customHeight="1">
-      <c r="A24" s="6" t="n"/>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6" t="n"/>
-      <c r="G24" s="6" t="n"/>
-      <c r="H24" s="6" t="n"/>
-      <c r="I24" s="6" t="n"/>
-      <c r="J24" s="6" t="n"/>
-      <c r="K24" s="6" t="n"/>
-      <c r="L24" s="7" t="n"/>
-      <c r="M24" s="7" t="n"/>
-      <c r="N24" s="7" t="n"/>
-      <c r="O24" s="7" t="n"/>
-    </row>
-    <row r="25" ht="50" customHeight="1">
-      <c r="A25" s="6" t="n"/>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="n"/>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
-      <c r="I25" s="6" t="n"/>
-      <c r="J25" s="6" t="n"/>
-      <c r="K25" s="6" t="n"/>
-      <c r="L25" s="7" t="n"/>
-      <c r="M25" s="7" t="n"/>
-      <c r="N25" s="7" t="n"/>
-      <c r="O25" s="7" t="n"/>
-    </row>
-    <row r="26" ht="50" customHeight="1">
-      <c r="A26" s="6" t="n"/>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
-      <c r="I26" s="6" t="n"/>
-      <c r="J26" s="6" t="n"/>
-      <c r="K26" s="6" t="n"/>
-      <c r="L26" s="7" t="n"/>
-      <c r="M26" s="7" t="n"/>
-      <c r="N26" s="7" t="n"/>
-      <c r="O26" s="7" t="n"/>
-    </row>
-    <row r="27" ht="50" customHeight="1">
-      <c r="A27" s="6" t="n"/>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
-      <c r="I27" s="6" t="n"/>
-      <c r="J27" s="6" t="n"/>
-      <c r="K27" s="6" t="n"/>
-      <c r="L27" s="7" t="n"/>
-      <c r="M27" s="7" t="n"/>
-      <c r="N27" s="7" t="n"/>
-      <c r="O27" s="7" t="n"/>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>【訪問職種凡例】看：看護師　准：准看護師　PT：理学療法士　OT：作業療法士　ST：言語聴覚士　【疼痛NRS】0=痛みなし〜10=最大の痛み　【意識JCS】0=清明　1〜3桁=障害あり</t>
-        </is>
-      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>※ 記録は客観的事実を中心に。指示内容・利用者や家族の反応・次回への申し送りも記載。改ざん防止のため修正は二重線＋訂正印。</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="8" t="n"/>
+      <c r="H21" s="8" t="n"/>
+      <c r="I21" s="8" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="A28:O28"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="I3:J3"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>